--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <v>42</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>31</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>206</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.6456310679611651</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>108</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.3888888888888889</v>
+        <v>42</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR DI VIRGILIO DAVID.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
